--- a/Grids Germany/No leap years/Saxony insights/[Saxony][Manhattan][Raw]Aggregated_U_test.xlsx
+++ b/Grids Germany/No leap years/Saxony insights/[Saxony][Manhattan][Raw]Aggregated_U_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean_P1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Mean_P2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>SD_P1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SD_P2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Median_P1</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Median_P2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Median_difference_P2_minus_P1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>p_Bonferroni</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -495,40 +507,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1500</v>
+        <v>1470</v>
       </c>
       <c r="C2" t="n">
         <v>450</v>
       </c>
       <c r="D2" t="n">
-        <v>10.11891108024901</v>
+        <v>10.05292288089254</v>
       </c>
       <c r="E2" t="n">
-        <v>12.3188039300254</v>
+        <v>12.20395206380251</v>
       </c>
       <c r="F2" t="n">
-        <v>4.399661228901839</v>
+        <v>4.41299201196736</v>
       </c>
       <c r="G2" t="n">
-        <v>3.169377803474045</v>
+        <v>3.144718610933814</v>
       </c>
       <c r="H2" t="n">
-        <v>10.21883283498765</v>
+        <v>10.10929043474335</v>
       </c>
       <c r="I2" t="n">
-        <v>11.97717161633965</v>
+        <v>11.83877430349885</v>
       </c>
       <c r="J2" t="n">
-        <v>1.758338781352</v>
+        <v>1.7294838687555</v>
       </c>
       <c r="K2" t="n">
-        <v>237783</v>
+        <v>234677</v>
       </c>
       <c r="L2" t="n">
-        <v>1.75377828029617e-21</v>
+        <v>1.000369589591642e-20</v>
       </c>
       <c r="M2" t="n">
-        <v>7.01511312118468e-21</v>
+        <v>4.001478358366569e-20</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -541,40 +553,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1500</v>
+        <v>1470</v>
       </c>
       <c r="C3" t="n">
         <v>450</v>
       </c>
       <c r="D3" t="n">
-        <v>70.32392304365393</v>
+        <v>70.21689550741576</v>
       </c>
       <c r="E3" t="n">
-        <v>79.1416327184035</v>
+        <v>79.34910716653204</v>
       </c>
       <c r="F3" t="n">
-        <v>11.3804257535376</v>
+        <v>11.40084541872801</v>
       </c>
       <c r="G3" t="n">
-        <v>8.340641320611645</v>
+        <v>8.289075840424637</v>
       </c>
       <c r="H3" t="n">
-        <v>70.34167636427405</v>
+        <v>70.21177452270621</v>
       </c>
       <c r="I3" t="n">
-        <v>79.68232877356606</v>
+        <v>79.86307319178745</v>
       </c>
       <c r="J3" t="n">
-        <v>9.340652409292005</v>
+        <v>9.651298669081243</v>
       </c>
       <c r="K3" t="n">
-        <v>181914</v>
+        <v>173540</v>
       </c>
       <c r="L3" t="n">
-        <v>6.772099696455095e-50</v>
+        <v>1.086770669122771e-52</v>
       </c>
       <c r="M3" t="n">
-        <v>2.708839878582038e-49</v>
+        <v>4.347082676491083e-52</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -587,40 +599,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1500</v>
+        <v>1470</v>
       </c>
       <c r="C4" t="n">
         <v>450</v>
       </c>
       <c r="D4" t="n">
-        <v>12.42278545243824</v>
+        <v>12.349449084079</v>
       </c>
       <c r="E4" t="n">
-        <v>13.99982639947584</v>
+        <v>13.82696573717338</v>
       </c>
       <c r="F4" t="n">
-        <v>4.289802357054353</v>
+        <v>4.268894948340217</v>
       </c>
       <c r="G4" t="n">
-        <v>2.687843635113467</v>
+        <v>2.673152614365606</v>
       </c>
       <c r="H4" t="n">
-        <v>12.506223560039</v>
+        <v>12.4319882850634</v>
       </c>
       <c r="I4" t="n">
-        <v>13.7422307191669</v>
+        <v>13.6796452977546</v>
       </c>
       <c r="J4" t="n">
-        <v>1.236007159127901</v>
+        <v>1.247657012691199</v>
       </c>
       <c r="K4" t="n">
-        <v>263320</v>
+        <v>261937</v>
       </c>
       <c r="L4" t="n">
-        <v>1.431278525688379e-12</v>
+        <v>2.278390927504367e-11</v>
       </c>
       <c r="M4" t="n">
-        <v>5.725114102753517e-12</v>
+        <v>9.113563710017468e-11</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -633,40 +645,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1500</v>
+        <v>1470</v>
       </c>
       <c r="C5" t="n">
         <v>450</v>
       </c>
       <c r="D5" t="n">
-        <v>90.04705477497856</v>
+        <v>90.08427267493447</v>
       </c>
       <c r="E5" t="n">
-        <v>76.61695000157232</v>
+        <v>77.47328602069362</v>
       </c>
       <c r="F5" t="n">
-        <v>21.60781367916957</v>
+        <v>21.64905548043298</v>
       </c>
       <c r="G5" t="n">
-        <v>31.06531346200452</v>
+        <v>30.43004764653183</v>
       </c>
       <c r="H5" t="n">
-        <v>91.53645909991505</v>
+        <v>91.5073535239173</v>
       </c>
       <c r="I5" t="n">
-        <v>78.30324653269174</v>
+        <v>80.26332861590714</v>
       </c>
       <c r="J5" t="n">
-        <v>-13.2332125672233</v>
+        <v>-11.24402490801016</v>
       </c>
       <c r="K5" t="n">
-        <v>420359</v>
+        <v>407486</v>
       </c>
       <c r="L5" t="n">
-        <v>2.584950839162353e-15</v>
+        <v>8.858159872960568e-14</v>
       </c>
       <c r="M5" t="n">
-        <v>1.033980335664941e-14</v>
+        <v>3.543263949184227e-13</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
